--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R7ddab4943f2a402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R102d9d0d9e4f46ec"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R102d9d0d9e4f46ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="R3be79d878ed144d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
   <x:si>
-    <x:t>Daily Holdings (%)  10/28/2026</x:t>
+    <x:t>Daily Holdings (%)  10/29/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -52,19 +52,19 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>66,045,042</x:t>
+    <x:t>65,555,336</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$14,224,781,145.96</x:t>
+    <x:t>$14,006,553,089.76</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>19.56%</x:t>
+    <x:t>19.62%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -76,13 +76,13 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>15,781,334</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,936,054,106.34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.54%</x:t>
+    <x:t>15,664,313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,764,006,996.53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.48%</x:t>
   </x:si>
   <x:si>
     <x:t>AMD</x:t>
@@ -94,13 +94,13 @@
     <x:t>BBG000BBQCY0</x:t>
   </x:si>
   <x:si>
-    <x:t>7,087,158</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$4,099,495,673.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.64%</x:t>
+    <x:t>7,034,604</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,984,540,397.68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.58%</x:t>
   </x:si>
   <x:si>
     <x:t>AVGO</x:t>
@@ -112,13 +112,13 @@
     <x:t>BBG00KHY5S69</x:t>
   </x:si>
   <x:si>
-    <x:t>11,524,558</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$4,054,454,749.98</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.58%</x:t>
+    <x:t>11,438,925</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,946,429,125.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.53%</x:t>
   </x:si>
   <x:si>
     <x:t>TXN</x:t>
@@ -130,13 +130,31 @@
     <x:t>BBG000BVV7G1</x:t>
   </x:si>
   <x:si>
-    <x:t>12,677,779</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,927,956,267.57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.40%</x:t>
+    <x:t>12,583,577</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,918,777,549.34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.49%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analog Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BB6G37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,893,136</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,419,937,966.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.79%</x:t>
   </x:si>
   <x:si>
     <x:t>MU</x:t>
@@ -148,31 +166,103 @@
     <x:t>BBG000C5Z1S3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,593,266</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,533,006,929.18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Analog Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BB6G37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,952,226</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,405,699,829.02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.68%</x:t>
+    <x:t>3,566,628</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,332,193,541.56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.67%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Asml Holding Nv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000K6MRN4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,907,529</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,196,446,345.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.48%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kla Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BMTFR4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,996,491</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,013,152,488.13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.22%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKHY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sk Hynix Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG0238L5JS9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,454,850</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,991,346,636.50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.19%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Applied Materials Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BBPFB9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,020,893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,960,429,742.38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.15%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qualcomm Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000CGC1X8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,625,474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,897,119,134.34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.06%</x:t>
   </x:si>
   <x:si>
     <x:t>MRVL</x:t>
@@ -184,49 +274,13 @@
     <x:t>BBG00ZXBJ153</x:t>
   </x:si>
   <x:si>
-    <x:t>13,176,503</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,315,866,979.95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.56%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASML</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Asml Holding Nv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000K6MRN4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,921,779</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,195,630,210.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.39%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKHY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sk Hynix Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG0238L5JS9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,592,714</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,062,219,995.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.21%</x:t>
+    <x:t>13,078,805</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,855,626,283.70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.00%</x:t>
   </x:si>
   <x:si>
     <x:t>INTC</x:t>
@@ -238,64 +292,10 @@
     <x:t>BBG000C0G1D1</x:t>
   </x:si>
   <x:si>
-    <x:t>31,215,813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,982,046,615.89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.10%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Applied Materials Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BBPFB9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,073,466</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,942,561,856.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.05%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qualcomm Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000CGC1X8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,742,457</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,880,397,357.29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.96%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kla Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BMTFR4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,131,220</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,878,693,799.40</x:t>
+    <x:t>30,983,842</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,852,682,332.94</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -307,13 +307,31 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>10,500,194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,665,159,241.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.66%</x:t>
+    <x:t>10,422,161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,651,293,536.79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.71%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Synopsys Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BSFRF3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,160,104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,549,051,379.76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.17%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -325,31 +343,13 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,519,571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,547,772,284.66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.13%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Synopsys Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BSFRF3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,183,759</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,534,221,624.51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.11%</x:t>
+    <x:t>4,485,979</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,537,569,302.25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.15%</x:t>
   </x:si>
   <x:si>
     <x:t>NXPI</x:t>
@@ -361,33 +361,33 @@
     <x:t>BBG000BND699</x:t>
   </x:si>
   <x:si>
-    <x:t>3,324,832</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$836,826,966.08</x:t>
+    <x:t>3,300,132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$877,835,112.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.23%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monolithic Power Systems Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000C30L48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>681,936</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$817,511,696.16</x:t>
   </x:si>
   <x:si>
     <x:t>1.15%</x:t>
   </x:si>
   <x:si>
-    <x:t>MPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Monolithic Power Systems Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000C30L48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>687,047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$832,165,067.34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.14%</x:t>
-  </x:si>
-  <x:si>
     <x:t>TER</x:t>
   </x:si>
   <x:si>
@@ -397,13 +397,13 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,439,019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$763,998,311.56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.05%</x:t>
+    <x:t>2,420,893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$717,141,133.39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.00%</x:t>
   </x:si>
   <x:si>
     <x:t>ALAB</x:t>
@@ -415,13 +415,13 @@
     <x:t>BBG00TDKHW99</x:t>
   </x:si>
   <x:si>
-    <x:t>2,460,376</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$731,223,747.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.01%</x:t>
+    <x:t>2,442,098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$709,258,522.14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.99%</x:t>
   </x:si>
   <x:si>
     <x:t>ARM</x:t>
@@ -433,13 +433,13 @@
     <x:t>BBG01J1GXZF0</x:t>
   </x:si>
   <x:si>
-    <x:t>3,029,378</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$714,630,270.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.98%</x:t>
+    <x:t>3,006,863</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$687,880,048.51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.96%</x:t>
   </x:si>
   <x:si>
     <x:t>STM</x:t>
@@ -451,13 +451,13 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>13,293,414</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$644,996,447.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.89%</x:t>
+    <x:t>13,194,633</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$659,599,703.67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.92%</x:t>
   </x:si>
   <x:si>
     <x:t>MCHP</x:t>
@@ -469,13 +469,13 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,811,200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$622,005,856.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.86%</x:t>
+    <x:t>7,753,155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$628,935,933.60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.88%</x:t>
   </x:si>
   <x:si>
     <x:t>ON</x:t>
@@ -487,10 +487,10 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,811,492</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$363,893,139.96</x:t>
+    <x:t>4,775,734</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$359,326,226.16</x:t>
   </x:si>
   <x:si>
     <x:t>0.50%</x:t>
@@ -502,13 +502,13 @@
     <x:t> </x:t>
   </x:si>
   <x:si>
-    <x:t>45,116,698</x:t>
+    <x:t>45,136,304</x:t>
   </x:si>
   <x:si>
     <x:t>Cash Bal</x:t>
   </x:si>
   <x:si>
-    <x:t>$45,116,698.02</x:t>
+    <x:t>$45,136,303.90</x:t>
   </x:si>
   <x:si>
     <x:t>0.06%</x:t>
@@ -520,10 +520,10 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-15,522,253.13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-0.02%</x:t>
+    <x:t>$2,919,754.47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.00%</x:t>
   </x:si>
   <x:si>
     <x:t>These are not recommendations to buy or to sell any security. Securities and holdings may vary.</x:t>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="R3be79d878ed144d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="R2ee22cd0b3d94f19"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="R2ee22cd0b3d94f19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="R804f851afced4079"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="R804f851afced4079"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="Rb85feb2980874fe4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-30.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="Rb85feb2980874fe4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261029" sheetId="1" r:id="Rf770fcec7efb4cea"/>
   </x:sheets>
 </x:workbook>
 </file>
